--- a/src/main/webapp/xlsxTemplates/图纸.xlsx
+++ b/src/main/webapp/xlsxTemplates/图纸.xlsx
@@ -60,10 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>上传文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -72,7 +68,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自动填充</t>
+    <t>空/文件名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>录入者名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -126,7 +126,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -413,6 +413,8 @@
     <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="9.109375" customWidth="1"/>
     <col min="5" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -435,10 +437,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
         <v>11</v>
-      </c>
-      <c r="H1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -452,16 +454,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="2">
-        <v>45909</v>
+        <v>20250909</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
